--- a/backups/CVR_Weekly_Backup_20_08_2026.xlsx
+++ b/backups/CVR_Weekly_Backup_20_08_2026.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -428,88 +428,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>TOTAL</v>
       </c>
       <c r="B2" t="str">
-        <v>20/08/2026</v>
+        <v>0 Rows</v>
       </c>
       <c r="C2" t="str">
-        <v>Admin</v>
+        <v>Total Collection</v>
       </c>
       <c r="D2">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>State Bank of India (SBI)</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>Admin</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>20/08/2026</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="D3">
-        <v>400</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Canara Bank</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Admin</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>20/08/2026</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="D4">
-        <v>400</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Canara Bank</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Admin</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TOTAL</v>
-      </c>
-      <c r="B5" t="str">
-        <v>3 Rows</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Total Collection</v>
-      </c>
-      <c r="D5">
-        <v>90800</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>